--- a/sampleprojects/SinusitisTherapy/excel/sinusitis.xlsx
+++ b/sampleprojects/SinusitisTherapy/excel/sinusitis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
   <si>
     <t>EDD: EDD</t>
   </si>
@@ -202,12 +202,33 @@
     <t>Patient age in years</t>
   </si>
   <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>Patient age?</t>
+  </si>
+  <si>
+    <t>number</t>
+  </si>
+  <si>
+    <t>::years</t>
+  </si>
+  <si>
     <t>diagnosis</t>
   </si>
   <si>
+    <t>Acute Sinusitis</t>
+  </si>
+  <si>
     <t>Working diagnosis, e.g. Acute Sinusitis</t>
   </si>
   <si>
+    <t>Working diagnosis?</t>
+  </si>
+  <si>
+    <t>ascii</t>
+  </si>
+  <si>
     <t>lean_body_weight</t>
   </si>
   <si>
@@ -217,12 +238,24 @@
     <t>Lean body weight in kg (used by the CCr formula)</t>
   </si>
   <si>
+    <t>Lean body weight?</t>
+  </si>
+  <si>
+    <t>::kg</t>
+  </si>
+  <si>
     <t>pcr</t>
   </si>
   <si>
     <t>Plasma creatinine level (mg/dL)</t>
   </si>
   <si>
+    <t>Plasma creatinine (mg/dL)?</t>
+  </si>
+  <si>
+    <t>0.7:1.3:mg/dL</t>
+  </si>
+  <si>
     <t>penicillin_allergic</t>
   </si>
   <si>
@@ -233,6 +266,15 @@
   </si>
   <si>
     <t>True if the patient is penicillin-allergic</t>
+  </si>
+  <si>
+    <t>Is the patient penicillin-allergic?</t>
+  </si>
+  <si>
+    <t>multiple_choice</t>
+  </si>
+  <si>
+    <t>true=Yes|false=No</t>
   </si>
   <si>
     <t>result</t>
@@ -1332,19 +1374,19 @@
         <v>61</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="L17" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18">
@@ -1352,7 +1394,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>50</v>
@@ -1361,7 +1403,7 @@
         <v>16</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="F18" s="15" t="s">
         <v>51</v>
@@ -1370,16 +1412,16 @@
         <v>52</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="L18" s="7" t="s">
         <v>16</v>
@@ -1393,7 +1435,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>35</v>
@@ -1402,7 +1444,7 @@
         <v>16</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F19" s="15" t="s">
         <v>51</v>
@@ -1411,22 +1453,22 @@
         <v>52</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="L19" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20">
@@ -1434,7 +1476,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>35</v>
@@ -1443,7 +1485,7 @@
         <v>16</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F20" s="15" t="s">
         <v>51</v>
@@ -1452,22 +1494,22 @@
         <v>52</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="L20" s="7" t="s">
         <v>16</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21">
@@ -1475,16 +1517,16 @@
         <v>16</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F21" s="15" t="s">
         <v>51</v>
@@ -1493,19 +1535,19 @@
         <v>52</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="M21" s="8" t="s">
         <v>16</v>
@@ -1513,10 +1555,10 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
@@ -1535,7 +1577,7 @@
         <v>16</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>35</v>
@@ -1544,7 +1586,7 @@
         <v>16</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>16</v>
@@ -1553,7 +1595,7 @@
         <v>52</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>16</v>
@@ -1576,7 +1618,7 @@
         <v>16</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>18</v>
@@ -1591,10 +1633,10 @@
         <v>16</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="I24" s="8" t="s">
         <v>16</v>
@@ -1617,7 +1659,7 @@
         <v>16</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>18</v>
@@ -1632,10 +1674,10 @@
         <v>16</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="I25" s="7" t="s">
         <v>16</v>
@@ -1658,7 +1700,7 @@
         <v>16</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>18</v>
@@ -1673,10 +1715,10 @@
         <v>16</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="I26" s="8" t="s">
         <v>16</v>
@@ -1699,7 +1741,7 @@
         <v>16</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>57</v>
@@ -1717,7 +1759,7 @@
         <v>52</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="I27" s="7" t="s">
         <v>16</v>
@@ -1740,7 +1782,7 @@
         <v>16</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="C28" s="10" t="s">
         <v>50</v>
@@ -1758,7 +1800,7 @@
         <v>52</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="I28" s="8" t="s">
         <v>16</v>
@@ -1781,25 +1823,25 @@
         <v>16</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>16</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="I29" s="7" t="s">
         <v>16</v>
@@ -1822,7 +1864,7 @@
         <v>16</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="C30" s="14" t="s">
         <v>57</v>
@@ -1840,7 +1882,7 @@
         <v>52</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="I30" s="8" t="s">
         <v>16</v>
